--- a/sheets/대금율보/검수/사랑은 눈물의 씨앗.xlsx
+++ b/sheets/대금율보/검수/사랑은 눈물의 씨앗.xlsx
@@ -3657,8 +3657,7 @@
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太夾
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="G4" s="25"/>
@@ -3669,8 +3668,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∧
-‹</t>
+          <t xml:space="preserve">太∧</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
@@ -3820,8 +3818,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
@@ -3831,8 +3828,7 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -3904,8 +3900,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">林∧
-‹</t>
+          <t xml:space="preserve">林∧</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4047,8 +4042,7 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="I14" s="26"/>
@@ -4124,8 +4118,7 @@
       <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋
-㳞浹
-‹</t>
+㳞浹</t>
         </is>
       </c>
       <c r="I16" s="25"/>
@@ -4149,8 +4142,7 @@
       <c r="F17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–汰
-‹</t>
+–汰</t>
         </is>
       </c>
       <c r="G17" s="28" t="inlineStr">
@@ -4279,8 +4271,7 @@
       <c r="D21" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–汰
-‹</t>
+–汰</t>
         </is>
       </c>
       <c r="E21" s="25" t="inlineStr">
@@ -4328,8 +4319,7 @@
       <c r="F22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰無
-‹</t>
+汰無</t>
         </is>
       </c>
       <c r="G22" s="26"/>

--- a/sheets/대금율보/검수/사랑은 눈물의 씨앗.xlsx
+++ b/sheets/대금율보/검수/사랑은 눈물의 씨앗.xlsx
@@ -3564,20 +3564,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="83.33" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="74.53" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="I3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="74.53" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       <c r="H4" s="21"/>
       <c r="I4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="74.53" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="I5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="74.53" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="I6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="74.53" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="I7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="74.53" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="I8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="74.53" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="I9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="74.53" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="I10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="74.53" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="I11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="74.53" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="I12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="74.53" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="74.53" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="I14" s="26"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="74.53" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="I15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="74.53" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="I16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="74.53" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="I17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="74.53" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="I18" s="26"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="74.53" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="I19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="74.53" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="25"/>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="I20" s="25"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="74.53" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="I21" s="25"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="74.53" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -4337,6 +4337,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="48"/>
 </worksheet>
 </file>